--- a/public/exports-from-60-with-coowners/41333014.xlsx
+++ b/public/exports-from-60-with-coowners/41333014.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/41333014.xlsx
+++ b/public/exports-from-60-with-coowners/41333014.xlsx
@@ -266,17 +266,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blidstrupmark 24</t>
+          <t xml:space="preserve">Brogårdsvej 11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3441229</t>
+          <t xml:space="preserve">3444244</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -285,7 +285,7 @@
         </is>
       </c>
       <c r="J4">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -341,17 +341,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brogårdsvej 11</t>
+          <t xml:space="preserve">Bårupvej 43</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3444244</t>
+          <t xml:space="preserve">3436654</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -360,7 +360,7 @@
         </is>
       </c>
       <c r="J5">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -416,17 +416,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bårupvej 43</t>
+          <t xml:space="preserve">Elsøvej 10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436654</t>
+          <t xml:space="preserve">748001, 7343995</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="J6">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -506,11 +506,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J7">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsøvej 10</t>
+          <t xml:space="preserve">Elsøvej 8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -576,16 +576,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">748001, 7343995</t>
+          <t xml:space="preserve">748010, 10130755</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J8">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsøvej 8</t>
+          <t xml:space="preserve">Emilievej 11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -651,16 +651,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">748010, 10130755</t>
+          <t xml:space="preserve">747979, 5565046</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J9">
-        <v>96</v>
+        <v>614</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emilievej 11</t>
+          <t xml:space="preserve">Frederiksensvej 3A</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">747979, 5565046</t>
+          <t xml:space="preserve">3435860</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="J10">
-        <v>614</v>
+        <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -791,17 +791,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksensvej 3A</t>
+          <t xml:space="preserve">Fælleden 15A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3435860</t>
+          <t xml:space="preserve">748011, 7178370</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="J11">
-        <v>60</v>
+        <v>346</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -866,17 +866,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fælleden 15A</t>
+          <t xml:space="preserve">Glomstrupvej 9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7970</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">748011, 7178370</t>
+          <t xml:space="preserve">3442325</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="J12">
-        <v>346</v>
+        <v>133</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -941,17 +941,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glomstrupvej 9</t>
+          <t xml:space="preserve">Gårdvejen 11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7970</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442325</t>
+          <t xml:space="preserve">3442976</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="J13">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gårdvejen 11</t>
+          <t xml:space="preserve">H. C. Ørsteds Vej 15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442976</t>
+          <t xml:space="preserve">748015, 9901894</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="J14">
-        <v>79</v>
+        <v>4466</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J15">
-        <v>4466</v>
+        <v>60</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. C. Ørsteds Vej 15</t>
+          <t xml:space="preserve">H. C. Ørsteds Vej 15A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1176,16 +1176,16 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">748015, 9901894</t>
+          <t xml:space="preserve">9901894</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J16">
-        <v>60</v>
+        <v>424</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. C. Ørsteds Vej 15A</t>
+          <t xml:space="preserve">Havnen 10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">9901894</t>
+          <t xml:space="preserve">10045441</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J17">
-        <v>424</v>
+        <v>220</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 10</t>
+          <t xml:space="preserve">Havnen 14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">10045441</t>
+          <t xml:space="preserve">747983, 5564792</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18">
-        <v>220</v>
+        <v>324</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 14</t>
+          <t xml:space="preserve">Havnen 1A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">747983, 5564792</t>
+          <t xml:space="preserve">5564805</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="J19">
-        <v>324</v>
+        <v>1100</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 1A</t>
+          <t xml:space="preserve">Havnen 6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564805</t>
+          <t xml:space="preserve">5564803</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="J20">
-        <v>1100</v>
+        <v>376</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 6</t>
+          <t xml:space="preserve">Havnen 8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564803</t>
+          <t xml:space="preserve">5564804</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="J21">
-        <v>376</v>
+        <v>722</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1616,26 +1616,26 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 8</t>
+          <t xml:space="preserve">Havnevej 75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564804</t>
+          <t xml:space="preserve">9481729</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J22">
-        <v>722</v>
+        <v>98</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 75</t>
+          <t xml:space="preserve">Havnevej 75A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J23">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 75A</t>
+          <t xml:space="preserve">Højrisvej 20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">9481729</t>
+          <t xml:space="preserve">3444286</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,17 +1841,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højrisvej 20</t>
+          <t xml:space="preserve">Karbymark 2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3444286</t>
+          <t xml:space="preserve">3442603</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="J25">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,17 +1916,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karbymark 2</t>
+          <t xml:space="preserve">Kirkebyen 37</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442603</t>
+          <t xml:space="preserve">3439833</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="J26">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,17 +1991,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyen 37</t>
+          <t xml:space="preserve">Kjeldgårdsvej 19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3439833</t>
+          <t xml:space="preserve">9159769</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="J27">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldgårdsvej 19</t>
+          <t xml:space="preserve">Kjeldgårdsvej 29</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9159769</t>
+          <t xml:space="preserve">3444349</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="J28">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldgårdsvej 29</t>
+          <t xml:space="preserve">Kærvej 16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3444349</t>
+          <t xml:space="preserve">748008, 7885721</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="J29">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 16</t>
+          <t xml:space="preserve">Langebæksgade 30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">748008, 7885721</t>
+          <t xml:space="preserve">5566085</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="J30">
-        <v>265</v>
+        <v>145</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebæksgade 30</t>
+          <t xml:space="preserve">Langebæksgade 32</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566085</t>
+          <t xml:space="preserve">5566086</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="J31">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebæksgade 32</t>
+          <t xml:space="preserve">Langelinie 25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566086</t>
+          <t xml:space="preserve">747985, 5566047</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="J32">
-        <v>109</v>
+        <v>593</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelinie 25</t>
+          <t xml:space="preserve">Markedsgade 50</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">747985, 5566047</t>
+          <t xml:space="preserve">5564299</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="J33">
-        <v>593</v>
+        <v>86</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedsgade 50</t>
+          <t xml:space="preserve">Mælkevejen 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564299</t>
+          <t xml:space="preserve">3447941</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J34">
-        <v>86</v>
+        <v>345</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 1</t>
+          <t xml:space="preserve">Mælkevejen 3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3447941</t>
+          <t xml:space="preserve">3447943</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="J35">
-        <v>345</v>
+        <v>88</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 3</t>
+          <t xml:space="preserve">Næssundvej 351</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3447943</t>
+          <t xml:space="preserve">3442183</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="J36">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 351</t>
+          <t xml:space="preserve">Næssundvej 386</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442183</t>
+          <t xml:space="preserve">3442749</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="J37">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 386</t>
+          <t xml:space="preserve">Nørrealle 26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7980</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442749</t>
+          <t xml:space="preserve">3446287</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="J38">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2891,26 +2891,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrealle 26</t>
+          <t xml:space="preserve">Pavillonvej 7A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3446287</t>
+          <t xml:space="preserve">5566041</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J39">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2966,26 +2966,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavillonvej 7A</t>
+          <t xml:space="preserve">Præstbrovej 40</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566041</t>
+          <t xml:space="preserve">3436927</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3041,26 +3041,26 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstbrovej 40</t>
+          <t xml:space="preserve">Rolstrupvej 9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436927</t>
+          <t xml:space="preserve">8765700</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J41">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupvej 9</t>
+          <t xml:space="preserve">Strandvejen 4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,16 +3126,16 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8765700</t>
+          <t xml:space="preserve">5564808</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 4</t>
+          <t xml:space="preserve">Strandvejen 55</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564808</t>
+          <t xml:space="preserve">747991, 5566052</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="J43">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 55</t>
+          <t xml:space="preserve">Strandvejen 57</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">747991, 5566052</t>
+          <t xml:space="preserve">747996, 5566051</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="J44">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 57</t>
+          <t xml:space="preserve">Teglgårdsvej 24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">747996, 5566051</t>
+          <t xml:space="preserve">748019, 9847052</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="J45">
-        <v>76</v>
+        <v>376</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgårdsvej 24</t>
+          <t xml:space="preserve">Torvegade 21A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,16 +3426,16 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">748019, 9847052</t>
+          <t xml:space="preserve">3437509</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 21A</t>
+          <t xml:space="preserve">Torvegade 27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,16 +3501,16 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437509</t>
+          <t xml:space="preserve">3437563</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 27</t>
+          <t xml:space="preserve">Vestergade 16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,16 +3576,16 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3437563</t>
+          <t xml:space="preserve">747987, 100008631</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J48">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3641,26 +3641,26 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 16</t>
+          <t xml:space="preserve">Årbækmøllevej 14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">747987, 100008631</t>
+          <t xml:space="preserve">747993, 3446637</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J49">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Årbækmøllevej 14</t>
+          <t xml:space="preserve">Ørndrupvej 48</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">747993, 3446637</t>
+          <t xml:space="preserve">3442439</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="J50">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørndrupvej 48</t>
+          <t xml:space="preserve">Ørndrupvej 50</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442439</t>
+          <t xml:space="preserve">3442434</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="J51">
-        <v>129</v>
+        <v>1074</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,26 +3866,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørndrupvej 50</t>
+          <t xml:space="preserve">Øroddevej 100A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442434</t>
+          <t xml:space="preserve">747990, 8804642</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J52">
-        <v>1074</v>
+        <v>364</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3956,11 +3956,11 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J53">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øroddevej 100A</t>
+          <t xml:space="preserve">Øroddevej 80A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,16 +4026,16 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">747990, 8804642</t>
+          <t xml:space="preserve">747989, 8303330</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J54">
-        <v>80</v>
+        <v>1093</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øroddevej 80A</t>
+          <t xml:space="preserve">Øroddevej 80C</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4106,11 +4106,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J55">
-        <v>1093</v>
+        <v>588</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øroddevej 80C</t>
+          <t xml:space="preserve">Østervang 66</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,16 +4176,16 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">747989, 8303330</t>
+          <t xml:space="preserve">3441748</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>588</v>
+        <v>103</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 66</t>
+          <t xml:space="preserve">Grønnegade 10A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3441748</t>
+          <t xml:space="preserve">100003703</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J57">
-        <v>103</v>
+        <v>390</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200026671</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-01-13</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10A</t>
+          <t xml:space="preserve">Jantevej 3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,30 +4326,30 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003703</t>
+          <t xml:space="preserve">3435230</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>390</v>
+        <v>142</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026671</t>
+          <t xml:space="preserve">311006941</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-13</t>
+          <t xml:space="preserve">2023-07-02</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,40 +4391,40 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jantevej 3</t>
+          <t xml:space="preserve">Smedebjergevej 51A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7980</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3435230</t>
+          <t xml:space="preserve">3445775</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J59">
-        <v>142</v>
+        <v>894</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311006941</t>
+          <t xml:space="preserve">311093480</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">EnergiConsult</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-02</t>
+          <t xml:space="preserve">2025-01-30</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 51A</t>
+          <t xml:space="preserve">Smedebjergevej 51B</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>894</v>
+        <v>1064</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 51B</t>
+          <t xml:space="preserve">Smedebjergevej 51C</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J61">
-        <v>1064</v>
+        <v>898</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,30 +4616,30 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 51C</t>
+          <t xml:space="preserve">Rolstrupparken 1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445775</t>
+          <t xml:space="preserve">7896534</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>898</v>
+        <v>453</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311093480</t>
+          <t xml:space="preserve">311110782</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-30</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">H. C. Ørsteds Vej 2D</t>
+          <t xml:space="preserve">Rolstrupvej 10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7927126</t>
+          <t xml:space="preserve">5568835</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>653</v>
+        <v>764</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110803</t>
+          <t xml:space="preserve">311112752</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-13</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupparken 1</t>
+          <t xml:space="preserve">Bygaden 31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896534</t>
+          <t xml:space="preserve">3447005</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>453</v>
+        <v>235</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110782</t>
+          <t xml:space="preserve">311120872</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-06-23</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupvej 10</t>
+          <t xml:space="preserve">Feggesundvej 53</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5568835</t>
+          <t xml:space="preserve">1429901</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J65">
-        <v>764</v>
+        <v>145</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112752</t>
+          <t xml:space="preserve">311124391</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-13</t>
+          <t xml:space="preserve">2025-07-10</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 31</t>
+          <t xml:space="preserve">Næssundvej 325</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3447005</t>
+          <t xml:space="preserve">3442200</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>235</v>
+        <v>1509</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311120872</t>
+          <t xml:space="preserve">311143918</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-23</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feggesundvej 53</t>
+          <t xml:space="preserve">Skovparken 1A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,30 +5001,30 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429901</t>
+          <t xml:space="preserve">5563842</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>145</v>
+        <v>949</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124391</t>
+          <t xml:space="preserve">311157673</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-10</t>
+          <t xml:space="preserve">2026-02-08</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 325</t>
+          <t xml:space="preserve">Holgersgade 1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442200</t>
+          <t xml:space="preserve">8283248</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,31 +5085,31 @@
         </is>
       </c>
       <c r="J68">
-        <v>1509</v>
+        <v>1029</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311143918</t>
+          <t xml:space="preserve">311218644</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovparken 1A</t>
+          <t xml:space="preserve">Holgersgade 3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563842</t>
+          <t xml:space="preserve">8741158</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,31 +5160,31 @@
         </is>
       </c>
       <c r="J69">
-        <v>949</v>
+        <v>782</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311157673</t>
+          <t xml:space="preserve">311218646</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-08</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5216,17 +5216,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 1</t>
+          <t xml:space="preserve">Sundbyvej 15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8283248</t>
+          <t xml:space="preserve">3440481</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5235,21 +5235,21 @@
         </is>
       </c>
       <c r="J70">
-        <v>1029</v>
+        <v>129</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218644</t>
+          <t xml:space="preserve">311285722</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">Engko Aps</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-11-24</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsø Kommune</t>
+          <t xml:space="preserve">Region Nordjylland</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 3</t>
+          <t xml:space="preserve">Asylgade 21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,30 +5301,30 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741158</t>
+          <t xml:space="preserve">8741160</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J71">
-        <v>782</v>
+        <v>130</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218646</t>
+          <t xml:space="preserve">311287324</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morsø Kommune</t>
+          <t xml:space="preserve">Region Nordjylland</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundbyvej 15</t>
+          <t xml:space="preserve">Asylgade 25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3440481</t>
+          <t xml:space="preserve">8741160</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,21 +5385,21 @@
         </is>
       </c>
       <c r="J72">
-        <v>129</v>
+        <v>2702</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285722</t>
+          <t xml:space="preserve">311287323</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engko Aps</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-24</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 21</t>
+          <t xml:space="preserve">Strandparken 48</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741160</t>
+          <t xml:space="preserve">5565403</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="J73">
-        <v>130</v>
+        <v>3011</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287324</t>
+          <t xml:space="preserve">311287415</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 25</t>
+          <t xml:space="preserve">Strandparken 48</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5526,20 +5526,20 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741160</t>
+          <t xml:space="preserve">5565403</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J74">
-        <v>2702</v>
+        <v>956</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287323</t>
+          <t xml:space="preserve">311287416</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-06</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5606,15 +5606,15 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J75">
-        <v>3011</v>
+        <v>1593</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287415</t>
+          <t xml:space="preserve">311287418</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region Nordjylland</t>
+          <t xml:space="preserve">Morsø Kommune</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5666,40 +5666,40 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandparken 48</t>
+          <t xml:space="preserve">Vindbakken 6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7970</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5565403</t>
+          <t xml:space="preserve">3444980</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>956</v>
+        <v>1644</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287416</t>
+          <t xml:space="preserve">311291681</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2028-01-09</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Region Nordjylland</t>
+          <t xml:space="preserve">Morsø Kommune</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5741,40 +5741,40 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandparken 48</t>
+          <t xml:space="preserve">Nordmorsvej 43</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5565403</t>
+          <t xml:space="preserve">3435574</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77">
-        <v>1593</v>
+        <v>116</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287418</t>
+          <t xml:space="preserve">311301905</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-06</t>
+          <t xml:space="preserve">2028-03-09</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindbakken 6</t>
+          <t xml:space="preserve">Riis Alle 33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7970</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3444980</t>
+          <t xml:space="preserve">100199383</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>1644</v>
+        <v>3650</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291681</t>
+          <t xml:space="preserve">311511485</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-09</t>
+          <t xml:space="preserve">2031-04-12</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,17 +5891,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordmorsvej 43</t>
+          <t xml:space="preserve">Skovgade 17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">3435574</t>
+          <t xml:space="preserve">5563837</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="J79">
-        <v>116</v>
+        <v>916</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311301905</t>
+          <t xml:space="preserve">311630222</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-09</t>
+          <t xml:space="preserve">2032-09-22</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 33</t>
+          <t xml:space="preserve">Limfjordsvej 95A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100199383</t>
+          <t xml:space="preserve">383950, 383951, 383952, 383953, 100226311</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>3650</v>
+        <v>12832</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511485</t>
+          <t xml:space="preserve">311655787</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-12</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgade 17</t>
+          <t xml:space="preserve">Ringsgade 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563837</t>
+          <t xml:space="preserve">5563951</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J81">
-        <v>916</v>
+        <v>402</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311630222</t>
+          <t xml:space="preserve">311689354</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-22</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Limfjordsvej 95A</t>
+          <t xml:space="preserve">Nørregade 18A</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">383950, 383951, 383952, 383953, 100226311</t>
+          <t xml:space="preserve">5563734, 100939597</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>12832</v>
+        <v>116</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655787</t>
+          <t xml:space="preserve">311705508</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-09-06</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringsgade 3</t>
+          <t xml:space="preserve">Præstealle 1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563951</t>
+          <t xml:space="preserve">8783252</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J83">
-        <v>402</v>
+        <v>206</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689354</t>
+          <t xml:space="preserve">311735276</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 18A</t>
+          <t xml:space="preserve">Præstealle 1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563734, 100939597</t>
+          <t xml:space="preserve">8783252</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J84">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311705435</t>
+          <t xml:space="preserve">311735275</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-06</t>
+          <t xml:space="preserve">2034-01-26</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,40 +6341,40 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstealle 1</t>
+          <t xml:space="preserve">Utkærvej 3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8783252</t>
+          <t xml:space="preserve">3436238</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735276</t>
+          <t xml:space="preserve">311772162</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2034-07-08</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstealle 1</t>
+          <t xml:space="preserve">Nørrebro 140</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8783252</t>
+          <t xml:space="preserve">5566277</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735275</t>
+          <t xml:space="preserve">311773845</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-26</t>
+          <t xml:space="preserve">2034-07-17</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Utkærvej 3</t>
+          <t xml:space="preserve">Nørrebro 140</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,30 +6501,30 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436238</t>
+          <t xml:space="preserve">5566277</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J87">
-        <v>158</v>
+        <v>370</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772162</t>
+          <t xml:space="preserve">311773845</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-08</t>
+          <t xml:space="preserve">2034-07-17</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 140</t>
+          <t xml:space="preserve">Jernbanevej 5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566277</t>
+          <t xml:space="preserve">8730510</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J88">
-        <v>193</v>
+        <v>447</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773845</t>
+          <t xml:space="preserve">311786989</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-17</t>
+          <t xml:space="preserve">2034-09-24</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 140</t>
+          <t xml:space="preserve">Jernbanevej 7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566277</t>
+          <t xml:space="preserve">8730510</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>370</v>
+        <v>5671</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311773845</t>
+          <t xml:space="preserve">311786989</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-17</t>
+          <t xml:space="preserve">2034-09-24</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 5</t>
+          <t xml:space="preserve">Tranevej 2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730510</t>
+          <t xml:space="preserve">5568732</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>447</v>
+        <v>1128</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786989</t>
+          <t xml:space="preserve">311807701</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-24</t>
+          <t xml:space="preserve">2035-01-24</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 7</t>
+          <t xml:space="preserve">Duevej 9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8730510</t>
+          <t xml:space="preserve">5567529</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>5671</v>
+        <v>9790</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786989</t>
+          <t xml:space="preserve">311809736</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-24</t>
+          <t xml:space="preserve">2035-02-04</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 2</t>
+          <t xml:space="preserve">Nygade 29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5568732</t>
+          <t xml:space="preserve">5563499</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>1128</v>
+        <v>2577</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807701</t>
+          <t xml:space="preserve">311824434</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-24</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 9</t>
+          <t xml:space="preserve">Støberivej 11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567529</t>
+          <t xml:space="preserve">8802259</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J93">
-        <v>9790</v>
+        <v>1110</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809736</t>
+          <t xml:space="preserve">311827910</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-04</t>
+          <t xml:space="preserve">2035-04-29</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 29</t>
+          <t xml:space="preserve">Støberivej 3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563499</t>
+          <t xml:space="preserve">8802259</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>2577</v>
+        <v>1110</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824434</t>
+          <t xml:space="preserve">311827910</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-04-29</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 11</t>
+          <t xml:space="preserve">Støberivej 5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 3</t>
+          <t xml:space="preserve">Støberivej 7</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7181,15 +7181,15 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>1110</v>
+        <v>1186</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827910</t>
+          <t xml:space="preserve">311827787</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 5</t>
+          <t xml:space="preserve">Støberivej 9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 7</t>
+          <t xml:space="preserve">Poulsen Dalsvej 4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8802259</t>
+          <t xml:space="preserve">1429816</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>1186</v>
+        <v>5427</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827787</t>
+          <t xml:space="preserve">311840748</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-29</t>
+          <t xml:space="preserve">2035-06-25</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Støberivej 9</t>
+          <t xml:space="preserve">Riis Alle 31D</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8802259</t>
+          <t xml:space="preserve">5567102</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>1110</v>
+        <v>293</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827910</t>
+          <t xml:space="preserve">311845015</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-29</t>
+          <t xml:space="preserve">2035-07-16</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,17 +7466,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poulsen Dalsvej 4</t>
+          <t xml:space="preserve">Riis Alle 31A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429816</t>
+          <t xml:space="preserve">5567102</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,11 +7485,11 @@
         </is>
       </c>
       <c r="J100">
-        <v>5427</v>
+        <v>650</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311840748</t>
+          <t xml:space="preserve">311845194</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-25</t>
+          <t xml:space="preserve">2035-07-17</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31D</t>
+          <t xml:space="preserve">Riis Alle 31B</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7556,15 +7556,15 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>293</v>
+        <v>650</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845015</t>
+          <t xml:space="preserve">311845194</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-16</t>
+          <t xml:space="preserve">2035-07-17</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31A</t>
+          <t xml:space="preserve">Riis Alle 31C</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J102">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31B</t>
+          <t xml:space="preserve">Rolstrupvej 1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567102</t>
+          <t xml:space="preserve">9622609</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>650</v>
+        <v>3693</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845194</t>
+          <t xml:space="preserve">311850483</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-17</t>
+          <t xml:space="preserve">2035-08-21</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,30 +7766,30 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riis Alle 31C</t>
+          <t xml:space="preserve">Næssundvej 348A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567102</t>
+          <t xml:space="preserve">3442077</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311845194</t>
+          <t xml:space="preserve">311851146</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-17</t>
+          <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolstrupvej 1</t>
+          <t xml:space="preserve">Næssundvej 348B</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7960</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622609</t>
+          <t xml:space="preserve">3442077</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>3693</v>
+        <v>520</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311850483</t>
+          <t xml:space="preserve">311851147</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-21</t>
+          <t xml:space="preserve">2035-08-25</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348A</t>
+          <t xml:space="preserve">Næssundvej 348C</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7931,15 +7931,15 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J106">
-        <v>630</v>
+        <v>520</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851146</t>
+          <t xml:space="preserve">311851147</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348B</t>
+          <t xml:space="preserve">Næssundvej 348D</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348C</t>
+          <t xml:space="preserve">Elsøvej 240</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442077</t>
+          <t xml:space="preserve">3441792</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>520</v>
+        <v>1569</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851147</t>
+          <t xml:space="preserve">311860707</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-25</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Næssundvej 348D</t>
+          <t xml:space="preserve">Bårupvej 15</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3442077</t>
+          <t xml:space="preserve">3436575</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>520</v>
+        <v>1826</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311851147</t>
+          <t xml:space="preserve">311862116</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-25</t>
+          <t xml:space="preserve">2035-10-15</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsøvej 240</t>
+          <t xml:space="preserve">Jernbanevej 9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3441792</t>
+          <t xml:space="preserve">5564812</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>1569</v>
+        <v>562</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860707</t>
+          <t xml:space="preserve">311865986</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-11-03</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bårupvej 15</t>
+          <t xml:space="preserve">Smallegade 10A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3436575</t>
+          <t xml:space="preserve">5563951</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>1826</v>
+        <v>177</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862116</t>
+          <t xml:space="preserve">311865984</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-15</t>
+          <t xml:space="preserve">2035-11-03</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 9</t>
+          <t xml:space="preserve">Smallegade 12A</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564812</t>
+          <t xml:space="preserve">5563951</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>562</v>
+        <v>187</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865986</t>
+          <t xml:space="preserve">311865984</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smallegade 10A</t>
+          <t xml:space="preserve">Skolestræde 11</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563951</t>
+          <t xml:space="preserve">3439180</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>177</v>
+        <v>611</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865984</t>
+          <t xml:space="preserve">311866171</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-03</t>
+          <t xml:space="preserve">2035-11-04</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smallegade 12A</t>
+          <t xml:space="preserve">Langebæksgade 34</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563951</t>
+          <t xml:space="preserve">10130755</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>187</v>
+        <v>350</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865984</t>
+          <t xml:space="preserve">311868326</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-03</t>
+          <t xml:space="preserve">2035-11-14</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestræde 11</t>
+          <t xml:space="preserve">Færøvej 1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3439180</t>
+          <t xml:space="preserve">9066233</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>611</v>
+        <v>1000</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311866171</t>
+          <t xml:space="preserve">311868564</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-04</t>
+          <t xml:space="preserve">2035-11-17</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebæksgade 34</t>
+          <t xml:space="preserve">Grønnegade 10A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130755</t>
+          <t xml:space="preserve">100003703</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>350</v>
+        <v>3187</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868326</t>
+          <t xml:space="preserve">311871957</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-14</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færøvej 1</t>
+          <t xml:space="preserve">Grønnegade 10A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9066233</t>
+          <t xml:space="preserve">100003703</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J117">
-        <v>1000</v>
+        <v>217</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868564</t>
+          <t xml:space="preserve">311871957</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-17</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>3187</v>
+        <v>1525</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8906,11 +8906,11 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J119">
-        <v>217</v>
+        <v>1920</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -8981,11 +8981,11 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J120">
-        <v>1525</v>
+        <v>208</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10A</t>
+          <t xml:space="preserve">Lundkjærvej 22</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003703</t>
+          <t xml:space="preserve">5567939</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>1920</v>
+        <v>343</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871957</t>
+          <t xml:space="preserve">311873042</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2035-12-11</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegade 10A</t>
+          <t xml:space="preserve">Maagevej 60A</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100003703</t>
+          <t xml:space="preserve">5567560</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871957</t>
+          <t xml:space="preserve">311876821</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundkjærvej 22</t>
+          <t xml:space="preserve">Maagevej 60D</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567939</t>
+          <t xml:space="preserve">5567560</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>343</v>
+        <v>262</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873042</t>
+          <t xml:space="preserve">311876821</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-11</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maagevej 60A</t>
+          <t xml:space="preserve">Maagevej 60E</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567560</t>
+          <t xml:space="preserve">8720449</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>131</v>
+        <v>297</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876821</t>
+          <t xml:space="preserve">311876820</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maagevej 60D</t>
+          <t xml:space="preserve">Nørregade 21</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,20 +9351,20 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5567560</t>
+          <t xml:space="preserve">5563641</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876821</t>
+          <t xml:space="preserve">311876983</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-16</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maagevej 60E</t>
+          <t xml:space="preserve">Færkenstræde 12</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8720449</t>
+          <t xml:space="preserve">5563666</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>297</v>
+        <v>115</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876820</t>
+          <t xml:space="preserve">311877227</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 21</t>
+          <t xml:space="preserve">Nørrebro 106</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563641</t>
+          <t xml:space="preserve">5564100</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>177</v>
+        <v>98</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876983</t>
+          <t xml:space="preserve">311877226</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-16</t>
+          <t xml:space="preserve">2036-01-19</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færkenstræde 12</t>
+          <t xml:space="preserve">Aagade 17</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563666</t>
+          <t xml:space="preserve">5563431</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311877227</t>
+          <t xml:space="preserve">311877727</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-19</t>
+          <t xml:space="preserve">2036-01-21</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebro 106</t>
+          <t xml:space="preserve">Smedebjergevej 49A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7980</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5564100</t>
+          <t xml:space="preserve">3445792</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J129">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311877226</t>
+          <t xml:space="preserve">311878772</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-19</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aagade 17</t>
+          <t xml:space="preserve">Smedebjergevej 49G</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7980</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5563431</t>
+          <t xml:space="preserve">3445792</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311877727</t>
+          <t xml:space="preserve">311878772</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-21</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,30 +9791,30 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 49A</t>
+          <t xml:space="preserve">Fredsøvej 49A</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445792</t>
+          <t xml:space="preserve">3443622</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>366</v>
+        <v>122</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878772</t>
+          <t xml:space="preserve">311879025</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebjergevej 49G</t>
+          <t xml:space="preserve">Fredsøvej 51A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7980</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445792</t>
+          <t xml:space="preserve">3443622</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J132">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878772</t>
+          <t xml:space="preserve">311879025</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-01-28</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredsøvej 49A</t>
+          <t xml:space="preserve">Fyrvejen 65</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3443622</t>
+          <t xml:space="preserve">9743167</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>122</v>
+        <v>1658</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879025</t>
+          <t xml:space="preserve">311882494</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-28</t>
+          <t xml:space="preserve">2036-02-17</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredsøvej 51A</t>
+          <t xml:space="preserve">Holgersgade 5A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3443622</t>
+          <t xml:space="preserve">8741159</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>122</v>
+        <v>1542</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311879025</t>
+          <t xml:space="preserve">311883270</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-28</t>
+          <t xml:space="preserve">2036-02-20</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvejen 65</t>
+          <t xml:space="preserve">Doktor Lunds Vej 3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7950</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9743167</t>
+          <t xml:space="preserve">100055624</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10110,21 +10110,21 @@
         </is>
       </c>
       <c r="J135">
-        <v>1658</v>
+        <v>2292</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882494</t>
+          <t xml:space="preserve">311906511</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-17</t>
+          <t xml:space="preserve">2036-06-08</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holgersgade 5A</t>
+          <t xml:space="preserve">Pavillonvej 7A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8741159</t>
+          <t xml:space="preserve">5566041</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>1542</v>
+        <v>150</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883270</t>
+          <t xml:space="preserve">311906951</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-20</t>
+          <t xml:space="preserve">2036-06-10</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,40 +10241,40 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doktor Lunds Vej 3</t>
+          <t xml:space="preserve">Havnevej 75</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7950</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100055624</t>
+          <t xml:space="preserve">9481729</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J137">
-        <v>2292</v>
+        <v>240</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311906511</t>
+          <t xml:space="preserve">311907302</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">KNN Energirådgivning, Vodskov Aps</t>
+          <t xml:space="preserve">EnergiConsult ApS</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-08</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pavillonvej 7A</t>
+          <t xml:space="preserve">Øroddevej 15</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566041</t>
+          <t xml:space="preserve">5566050</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>150</v>
+        <v>972</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311906951</t>
+          <t xml:space="preserve">311909858</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-10</t>
+          <t xml:space="preserve">2036-06-22</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 75</t>
+          <t xml:space="preserve">Tranevej 1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7990</t>
+          <t xml:space="preserve">7900</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9481729</t>
+          <t xml:space="preserve">8783288</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907302</t>
+          <t xml:space="preserve">311912759</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-07-03</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øroddevej 15</t>
+          <t xml:space="preserve">Holmen 3</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,20 +10476,20 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5566050</t>
+          <t xml:space="preserve">10045441</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J140">
-        <v>972</v>
+        <v>432</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311909858</t>
+          <t xml:space="preserve">311916673</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-22</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 1</t>
+          <t xml:space="preserve">Lupinvej 7A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8783288</t>
+          <t xml:space="preserve">7797589</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912759</t>
+          <t xml:space="preserve">311918686</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-03</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmen 3</t>
+          <t xml:space="preserve">Lupinvej 7B</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10045441</t>
+          <t xml:space="preserve">7797589</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J142">
-        <v>432</v>
+        <v>960</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916673</t>
+          <t xml:space="preserve">311918686</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7A</t>
+          <t xml:space="preserve">Lupinvej 7D</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>260</v>
+        <v>883</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7B</t>
+          <t xml:space="preserve">Lupinvej 7F</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,15 +10781,15 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J144">
-        <v>960</v>
+        <v>131</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918686</t>
+          <t xml:space="preserve">311918937</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-08-13</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7D</t>
+          <t xml:space="preserve">Skovvej 5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7797589</t>
+          <t xml:space="preserve">5565068</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J145">
-        <v>883</v>
+        <v>160</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918686</t>
+          <t xml:space="preserve">311919864</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lupinvej 7F</t>
+          <t xml:space="preserve">H. C. Ørsteds Vej 2D</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">7797589</t>
+          <t xml:space="preserve">7927126</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>131</v>
+        <v>653</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918937</t>
+          <t xml:space="preserve">311926925</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-13</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 5</t>
+          <t xml:space="preserve">Blidstrupmark 24</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7900</t>
+          <t xml:space="preserve">7990</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5565068</t>
+          <t xml:space="preserve">3441229</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,21 +11010,21 @@
         </is>
       </c>
       <c r="J147">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919864</t>
+          <t xml:space="preserve">311927730</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiConsult ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-18</t>
+          <t xml:space="preserve">2036-09-23</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">

--- a/public/exports-from-60-with-coowners/41333014.xlsx
+++ b/public/exports-from-60-with-coowners/41333014.xlsx
@@ -6139,7 +6139,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311705508</t>
+          <t xml:space="preserve">311705435</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
